--- a/wishlist_clara.xlsx
+++ b/wishlist_clara.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FC275E-0D92-4706-B274-D15CD9F44BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E74428-7A92-40DF-894E-B1FC9CC559C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="12645" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Clara" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Image</t>
   </si>
@@ -54,6 +54,42 @@
   </si>
   <si>
     <t>SKIP (skip: hide from display) / Y (reserved: show faded out) / GAP (formatting gap)</t>
+  </si>
+  <si>
+    <t>Voucher Fliplab</t>
+  </si>
+  <si>
+    <t>https://fliplab.ch/zurich/wp-content/uploads/2023/09/fliplab-logo-icon.svg</t>
+  </si>
+  <si>
+    <t>https://fliplab.ch/zurich/tickets-preise/</t>
+  </si>
+  <si>
+    <t>Voucher ZOO ZH</t>
+  </si>
+  <si>
+    <t>https://zoo-live.rokka.io/product_cropped_xs_1x/57ed224f1e21c761861be8eca1bdc1303224e9fe/geschenkkarte-2019-zoozuerich-01.png?itok=dUiUOVfF</t>
+  </si>
+  <si>
+    <t>https://www.zoo.ch/en/onlineshop/geschenkkarten/gift-card</t>
+  </si>
+  <si>
+    <t>Voucher Zalando</t>
+  </si>
+  <si>
+    <t>https://img01.ztat.net/article/spp-media-p1/47411619894742e0a3e7e3279001927d/53ad875805b34f7b8a81d3df7cea5f16.jpg?imwidth=300</t>
+  </si>
+  <si>
+    <t>https://www.zalando.ch/geschenk-gutscheine/</t>
+  </si>
+  <si>
+    <t>Trotinetă</t>
+  </si>
+  <si>
+    <t>Sicla apa</t>
+  </si>
+  <si>
+    <t>Haine masura 116</t>
   </si>
 </sst>
 </file>
@@ -420,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
@@ -443,6 +479,54 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/wishlist_clara.xlsx
+++ b/wishlist_clara.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E74428-7A92-40DF-894E-B1FC9CC559C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814FCC58-0DC9-4789-BD03-497052CCBDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="12645" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
@@ -83,13 +83,13 @@
     <t>https://www.zalando.ch/geschenk-gutscheine/</t>
   </si>
   <si>
-    <t>Trotinetă</t>
-  </si>
-  <si>
     <t>Sicla apa</t>
   </si>
   <si>
     <t>Haine masura 116</t>
+  </si>
+  <si>
+    <t>Trotineta</t>
   </si>
 </sst>
 </file>
@@ -516,17 +516,17 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/wishlist_clara.xlsx
+++ b/wishlist_clara.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814FCC58-0DC9-4789-BD03-497052CCBDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BE43C7-1364-4F4C-A899-40767C38307D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="12645" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="30240" yWindow="3375" windowWidth="21600" windowHeight="12645" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Clara" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Image</t>
   </si>
@@ -90,6 +90,18 @@
   </si>
   <si>
     <t>Trotineta</t>
+  </si>
+  <si>
+    <t>https://www.flikflak.com/de-ch/shine-in-rainbow-fpnp128/FPNP128.html</t>
+  </si>
+  <si>
+    <t>45 CHF</t>
+  </si>
+  <si>
+    <t>https://static.swatch.com/flikflak/images/product/ZFPNP128/fa200/ZFPNP128_fa200_er007m.png</t>
+  </si>
+  <si>
+    <t>Ceas</t>
   </si>
 </sst>
 </file>
@@ -456,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
@@ -483,56 +495,70 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E23" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D23">
-    <sortCondition ref="D2:D23"/>
+  <autoFilter ref="A1:E24" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D24">
+    <sortCondition ref="D3:D24"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/wishlist_clara.xlsx
+++ b/wishlist_clara.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BE43C7-1364-4F4C-A899-40767C38307D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{87BE43C7-1364-4F4C-A899-40767C38307D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA00262F-7466-4679-921B-95CA5DA31FA6}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="3375" windowWidth="21600" windowHeight="12645" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-28920" yWindow="7545" windowWidth="29040" windowHeight="16440" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Clara" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Image</t>
   </si>
@@ -83,9 +83,6 @@
     <t>https://www.zalando.ch/geschenk-gutscheine/</t>
   </si>
   <si>
-    <t>Sicla apa</t>
-  </si>
-  <si>
     <t>Haine masura 116</t>
   </si>
   <si>
@@ -102,13 +99,70 @@
   </si>
   <si>
     <t>Ceas</t>
+  </si>
+  <si>
+    <t>Sticla apa - una din cele trei</t>
+  </si>
+  <si>
+    <t>https://www.galaxus.ch/comparison/14065035-11241208-21089517</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/5SYmN8r.png</t>
+  </si>
+  <si>
+    <t>12 - 28</t>
+  </si>
+  <si>
+    <t>https://dthwkv5aeh23x.cloudfront.net/catalog/product/thumbnail/f4ea98919e0a2848bbd050a9454d9ef9a23c6db23843f1f682e2e9f1/image/322864/1000x1000/111/98/p/n/png-micro_sprite_led_neochrome-1.png</t>
+  </si>
+  <si>
+    <t>https://www.micro-scooter.com/ch_de/micro-sprite-led-neochrome</t>
+  </si>
+  <si>
+    <t>150 CHF</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/dp/B086JQQHPK?psc=1&amp;ref=cm_sw_r_cso_wa_apin_ct_T8G16RYHC41MDH4QNNWA&amp;social_share=cm_sw_r_cso_wa_apin_ct_T8G16RYHC41MDH4QNNWA</t>
+  </si>
+  <si>
+    <t>45 EUR</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71XVMb8RXAL._AC_SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>3Doodler</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/dp/B0G2L7GGQQ?ref=cm_sw_r_cso_wa_apin_ct_37N15CHN309FT5KWZP8D&amp;social_share=cm_sw_r_cso_wa_apin_ct_37N15CHN309FT5KWZP8D&amp;th=1</t>
+  </si>
+  <si>
+    <t>37 EUR</t>
+  </si>
+  <si>
+    <t>Potter's Wheel for Children</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/711tRaghf8L._AC_SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>Voucher intrare GrindelBoulder</t>
+  </si>
+  <si>
+    <t>https://grindelboulder.ch/medien/2025/07/Boulder-Kurs-fuer-Paare-Beitragsbild-768x512.jpg</t>
+  </si>
+  <si>
+    <t>https://grindelboulder.ch/preise-oeffnungszeiten/</t>
+  </si>
+  <si>
+    <t>12 CHF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +174,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -148,14 +210,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -468,11 +536,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
     <col min="3" max="3" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="3"/>
     <col min="5" max="5" width="79" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -486,7 +555,7 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -495,27 +564,30 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -531,28 +603,85 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>35</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -560,8 +689,12 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D24">
     <sortCondition ref="D3:D24"/>
   </sortState>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{3AC5649C-B5C2-4156-B142-DD20CC7C177C}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{3BE06934-14D4-4D9A-9F11-BBC44A53C79A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/wishlist_clara.xlsx
+++ b/wishlist_clara.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{87BE43C7-1364-4F4C-A899-40767C38307D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA00262F-7466-4679-921B-95CA5DA31FA6}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{87BE43C7-1364-4F4C-A899-40767C38307D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC79757-E3CE-4DF1-B0ED-CB1A19C2C924}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="7545" windowWidth="29040" windowHeight="16440" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Clara" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>Image</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>12 CHF</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
 </sst>
 </file>
@@ -214,11 +217,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
@@ -237,6 +238,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -541,7 +546,6 @@
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
     <col min="3" max="3" width="53.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="3"/>
     <col min="5" max="5" width="79" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -555,7 +559,7 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -572,7 +576,7 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -586,7 +590,7 @@
       <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -611,8 +615,11 @@
       <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" t="s">
         <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -625,7 +632,7 @@
       <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>32</v>
       </c>
     </row>
@@ -633,13 +640,13 @@
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -647,14 +654,17 @@
       <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" t="s">
         <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">

--- a/wishlist_clara.xlsx
+++ b/wishlist_clara.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\storage\OneDrive\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{87BE43C7-1364-4F4C-A899-40767C38307D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC79757-E3CE-4DF1-B0ED-CB1A19C2C924}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA6FA02-D4E7-415A-8E39-DA7CE1531605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="19740" yWindow="3570" windowWidth="43200" windowHeight="17145" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Clara" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>Image</t>
   </si>
@@ -238,10 +238,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -579,6 +575,9 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -593,6 +592,9 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -648,6 +650,9 @@
       </c>
       <c r="D7" t="s">
         <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">

--- a/wishlist_clara.xlsx
+++ b/wishlist_clara.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\storage\OneDrive\Downloads\wishlist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA6FA02-D4E7-415A-8E39-DA7CE1531605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABAA236-BD4D-4E29-8565-B7FFCF0D252F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19740" yWindow="3570" windowWidth="43200" windowHeight="17145" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Clara" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>Image</t>
   </si>
@@ -637,6 +637,9 @@
       <c r="D6" t="s">
         <v>32</v>
       </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
